--- a/summary_quarterly.xlsx
+++ b/summary_quarterly.xlsx
@@ -535,16 +535,16 @@
         <v>0.1238770856905482</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0002122977487451179</v>
+        <v>0.01243055109837092</v>
       </c>
       <c r="D5" t="n">
-        <v>0.93499931264518</v>
+        <v>0.5614535991343151</v>
       </c>
       <c r="E5" t="n">
         <v>0.5064988196722978</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1094465972119656</v>
+        <v>0.1822634912703819</v>
       </c>
       <c r="G5" t="n">
         <v>0.03756508775533993</v>
@@ -563,16 +563,16 @@
         <v>0.1136322568729118</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001732719905971953</v>
+        <v>0.01247877548620561</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9389968128763693</v>
+        <v>0.5654963020915034</v>
       </c>
       <c r="E6" t="n">
         <v>0.4602518417692139</v>
       </c>
       <c r="F6" t="n">
-        <v>0.09807026294883686</v>
+        <v>0.162843972641937</v>
       </c>
       <c r="G6" t="n">
         <v>0.03373856624632928</v>
@@ -591,16 +591,16 @@
         <v>0.1582840117130513</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0003274311693638618</v>
+        <v>0.01298051670437201</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9665720459545303</v>
+        <v>0.5814562366755565</v>
       </c>
       <c r="E7" t="n">
         <v>0.6614699859880879</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1414684189961328</v>
+        <v>0.2351671726299554</v>
       </c>
       <c r="G7" t="n">
         <v>0.05423098899480112</v>
@@ -619,16 +619,16 @@
         <v>0.1477820450074867</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0002938969577878758</v>
+        <v>0.0126696437322277</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9482215295151658</v>
+        <v>0.568676164644176</v>
       </c>
       <c r="E8" t="n">
         <v>0.6188644001585766</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1331307595873999</v>
+        <v>0.2219847785610422</v>
       </c>
       <c r="G8" t="n">
         <v>0.04904802108286583</v>
@@ -647,16 +647,16 @@
         <v>0.1235219020533762</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0002107492311603996</v>
+        <v>0.01237635424817078</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9308507955369588</v>
+        <v>0.5590357914074015</v>
       </c>
       <c r="E9" t="n">
         <v>0.5090232728205766</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1095527983821987</v>
+        <v>0.1824164232322882</v>
       </c>
       <c r="G9" t="n">
         <v>0.03779224438330132</v>
@@ -675,16 +675,16 @@
         <v>0.1490610468874636</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0002955912946805482</v>
+        <v>0.01284577088939121</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9606227777181371</v>
+        <v>0.5767035085694951</v>
       </c>
       <c r="E10" t="n">
         <v>0.6229258460124086</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1327435256785807</v>
+        <v>0.2211126730922096</v>
       </c>
       <c r="G10" t="n">
         <v>0.05058026119454025</v>
@@ -703,16 +703,16 @@
         <v>0.1468708778877921</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0002902401234882667</v>
+        <v>0.01262504851388172</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9440554404747791</v>
+        <v>0.5668078362834089</v>
       </c>
       <c r="E11" t="n">
         <v>0.6203323438087794</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1327530990115974</v>
+        <v>0.221108949698997</v>
       </c>
       <c r="G11" t="n">
         <v>0.04936424152854287</v>
@@ -731,16 +731,16 @@
         <v>0.1238770856905482</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0003275152750947078</v>
+        <v>0.01289900804266606</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8019911694481058</v>
+        <v>0.5807134834396771</v>
       </c>
       <c r="E12" t="n">
         <v>0.5064988196722978</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1275980298323763</v>
+        <v>0.1762185588638424</v>
       </c>
       <c r="G12" t="n">
         <v>0.06914657581830624</v>
@@ -759,16 +759,16 @@
         <v>0.1136322568729118</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0002906370906823887</v>
+        <v>0.0127873712198417</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7954506562173566</v>
+        <v>0.5772738949315847</v>
       </c>
       <c r="E13" t="n">
         <v>0.4602518417692139</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1157679154918472</v>
+        <v>0.1595216155717885</v>
       </c>
       <c r="G13" t="n">
         <v>0.06250030828985755</v>
@@ -787,16 +787,16 @@
         <v>0.1582840117130513</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0004492408544603877</v>
+        <v>0.0132114608101661</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8127988248687547</v>
+        <v>0.5895342599582375</v>
       </c>
       <c r="E14" t="n">
         <v>0.6614699859880879</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1682327963615407</v>
+        <v>0.2319448223360783</v>
       </c>
       <c r="G14" t="n">
         <v>0.08758654395227897</v>
@@ -815,16 +815,16 @@
         <v>0.1477820450074867</v>
       </c>
       <c r="C15" t="n">
-        <v>0.00041212281255623</v>
+        <v>0.01302372827069514</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8050256009051378</v>
+        <v>0.5825627191912346</v>
       </c>
       <c r="E15" t="n">
         <v>0.6188644001585766</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1568117241731741</v>
+        <v>0.2166933247234466</v>
       </c>
       <c r="G15" t="n">
         <v>0.08223412903173663</v>
@@ -843,16 +843,16 @@
         <v>0.1235219020533762</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0003262266340715594</v>
+        <v>0.0127719193019262</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7937878621638546</v>
+        <v>0.5749037935362489</v>
       </c>
       <c r="E16" t="n">
         <v>0.5090232728205766</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1284692225569953</v>
+        <v>0.177381521350041</v>
       </c>
       <c r="G16" t="n">
         <v>0.06768885361274873</v>
@@ -871,16 +871,16 @@
         <v>0.1490610468874636</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0004174631045960284</v>
+        <v>0.01300905799103805</v>
       </c>
       <c r="D17" t="n">
-        <v>0.802905454579294</v>
+        <v>0.5816449112997886</v>
       </c>
       <c r="E17" t="n">
         <v>0.6229258460124086</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1588187670592836</v>
+        <v>0.2192341957853615</v>
       </c>
       <c r="G17" t="n">
         <v>0.08050871589551681</v>
@@ -899,16 +899,16 @@
         <v>0.1468708778877921</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0004088144385580168</v>
+        <v>0.01289423008738642</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7962605600202732</v>
+        <v>0.5767391884404327</v>
       </c>
       <c r="E18" t="n">
         <v>0.6203323438087794</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1573935614224001</v>
+        <v>0.2173014906455063</v>
       </c>
       <c r="G18" t="n">
         <v>0.08052672169110162</v>
@@ -927,16 +927,16 @@
         <v>0.1238770856905482</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0001966273895103378</v>
+        <v>0.01161049466344297</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8406007956511355</v>
+        <v>0.5241802203598045</v>
       </c>
       <c r="E19" t="n">
         <v>0.5064988196722978</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1217373260814894</v>
+        <v>0.1952238737552884</v>
       </c>
       <c r="G19" t="n">
         <v>0.02754643408493343</v>
@@ -955,16 +955,16 @@
         <v>0.1136322568729118</v>
       </c>
       <c r="C20" t="n">
-        <v>0.000156992730957709</v>
+        <v>0.01167528913214327</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8459200229924955</v>
+        <v>0.5290111336878164</v>
       </c>
       <c r="E20" t="n">
         <v>0.4602518417692139</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1088609582985628</v>
+        <v>0.1740750968792439</v>
       </c>
       <c r="G20" t="n">
         <v>0.02380520296991184</v>
@@ -983,16 +983,16 @@
         <v>0.1582840117130513</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0003109019033067817</v>
+        <v>0.01214493217944482</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8700357926604262</v>
+        <v>0.5434984263337735</v>
       </c>
       <c r="E21" t="n">
         <v>0.6614699859880879</v>
       </c>
       <c r="F21" t="n">
-        <v>0.15716528025694</v>
+        <v>0.251591196150162</v>
       </c>
       <c r="G21" t="n">
         <v>0.04236467356486472</v>
@@ -1011,16 +1011,16 @@
         <v>0.1477820450074867</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0002774097928752573</v>
+        <v>0.01186307384924783</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8543831038522456</v>
+        <v>0.532053278328274</v>
       </c>
       <c r="E22" t="n">
         <v>0.6188644001585766</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1477527492202272</v>
+        <v>0.2372646831124164</v>
       </c>
       <c r="G22" t="n">
         <v>0.03784460006798984</v>
@@ -1039,16 +1039,16 @@
         <v>0.1235219020533762</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0001948924639977971</v>
+        <v>0.01157026293111767</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8376859698668524</v>
+        <v>0.5224134359709049</v>
       </c>
       <c r="E23" t="n">
         <v>0.5090232728205766</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1217369195565955</v>
+        <v>0.1952042242899917</v>
       </c>
       <c r="G23" t="n">
         <v>0.02761156102792353</v>
@@ -1067,16 +1067,16 @@
         <v>0.1490610468874636</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0002789385544227632</v>
+        <v>0.01202590596947863</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8653977401941704</v>
+        <v>0.5394738834973759</v>
       </c>
       <c r="E24" t="n">
         <v>0.6229258460124086</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1473501124845162</v>
+        <v>0.2363718768641325</v>
       </c>
       <c r="G24" t="n">
         <v>0.03894409055469463</v>
@@ -1095,16 +1095,16 @@
         <v>0.1468708778877921</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0002735946284971764</v>
+        <v>0.01183065491445858</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8513640232195087</v>
+        <v>0.5307531281289616</v>
       </c>
       <c r="E25" t="n">
         <v>0.6203323438087794</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1472064615648816</v>
+        <v>0.2361291506723517</v>
       </c>
       <c r="G25" t="n">
         <v>0.03791292317356407</v>
